--- a/Master/Opportunities_Data_Entry_Template.xlsx
+++ b/Master/Opportunities_Data_Entry_Template.xlsx
@@ -506,12 +506,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A23"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
@@ -625,7 +626,7 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>• Stage *: 01 Blue Sky Opportunity, 02 Identified Opportunity, 04 Proposal preparation, 05 Proposal submitted, 06 To Win, 07 Win, 08 Loss, 09 Client not interested, 10 Missed Opportunity</t>
+          <t>• Stage *: Blue Sky Opportunity, Identified Opportunity, Proposal preparation, Proposal submitted, To Win, Win, Loss, Client not interested, Missed Opportunity</t>
         </is>
       </c>
     </row>
@@ -702,22 +703,22 @@
           <t>BD owner *</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>Supporting role</t>
         </is>
       </c>
       <c r="G1" s="6" t="inlineStr">
         <is>
-          <t>Estimated value (USD) *</t>
+          <t>Estimated value (SGD) *</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>Probability (%)</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>Opportunity identified date</t>
         </is>
@@ -727,12 +728,12 @@
           <t>Discussion date *</t>
         </is>
       </c>
-      <c r="K1" s="7" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>Pitch date</t>
         </is>
       </c>
-      <c r="L1" s="7" t="inlineStr">
+      <c r="L1" s="6" t="inlineStr">
         <is>
           <t>Proposal submission date</t>
         </is>
@@ -742,7 +743,7 @@
           <t>Expected close date *</t>
         </is>
       </c>
-      <c r="N1" s="7" t="inlineStr">
+      <c r="N1" s="6" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -5644,7 +5645,7 @@
     <row r="2">
       <c r="D2" t="inlineStr">
         <is>
-          <t>01 Blue Sky Opportunity</t>
+          <t>Blue Sky Opportunity</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -5656,7 +5657,7 @@
     <row r="3">
       <c r="D3" t="inlineStr">
         <is>
-          <t>02 Identified Opportunity</t>
+          <t>Identified Opportunity</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -5668,7 +5669,7 @@
     <row r="4">
       <c r="D4" t="inlineStr">
         <is>
-          <t>04 Proposal preparation</t>
+          <t>Proposal preparation</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -5680,7 +5681,7 @@
     <row r="5">
       <c r="D5" t="inlineStr">
         <is>
-          <t>05 Proposal submitted</t>
+          <t>Proposal submitted</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -5692,35 +5693,35 @@
     <row r="6">
       <c r="D6" t="inlineStr">
         <is>
-          <t>06 To Win</t>
+          <t>To Win</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="D7" t="inlineStr">
         <is>
-          <t>07 Win</t>
+          <t>Win</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="D8" t="inlineStr">
         <is>
-          <t>08 Loss</t>
+          <t>Loss</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="D9" t="inlineStr">
         <is>
-          <t>09 Client not interested</t>
+          <t>Client not interested</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="D10" t="inlineStr">
         <is>
-          <t>10 Missed Opportunity</t>
+          <t>Missed Opportunity</t>
         </is>
       </c>
     </row>
